--- a/Assessment Questions/CDA/DAA-131/BREAK EVEN ANALYSIS/Preparing Data for Breakeven Analysis,/Preparing Data for Breakeven Analysis,.xlsx
+++ b/Assessment Questions/CDA/DAA-131/BREAK EVEN ANALYSIS/Preparing Data for Breakeven Analysis,/Preparing Data for Breakeven Analysis,.xlsx
@@ -1,168 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manfo\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D17C53C9-2406-4B55-A259-8416E5AD7FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BBC3C394-FB38-4B95-A2CF-270512F64FF3}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
-  <si>
-    <t>Type,Category,Item1,Item2,Item3,Item4,Item5</t>
-  </si>
-  <si>
-    <t>Data,Monthly,Jan,12500,8200,410,48</t>
-  </si>
-  <si>
-    <t>Data,Monthly,Feb,12800,9100,455,48</t>
-  </si>
-  <si>
-    <t>Data,Monthly,Mar,12400,7800,390,48</t>
-  </si>
-  <si>
-    <t>Data,Monthly,Apr,12900,9800,490,48</t>
-  </si>
-  <si>
-    <t>Data,Monthly,May,12600,8600,430,48</t>
-  </si>
-  <si>
-    <t>Data,Monthly,Jun,13000,10200,510,48</t>
-  </si>
-  <si>
-    <t>Data,Product,A,18,12,5,55</t>
-  </si>
-  <si>
-    <t>Data,Product,B,25,15,8,70</t>
-  </si>
-  <si>
-    <t>Data,Product,C,10,8,4,32</t>
-  </si>
-  <si>
-    <t>Data,Mixed,X,45000,28,65,OK</t>
-  </si>
-  <si>
-    <t>Data,Mixed,Y,38000,22,58,Good</t>
-  </si>
-  <si>
-    <t>Data,Mixed,Z,52000,35,72,High margin</t>
-  </si>
-  <si>
-    <t>Data,Mixed,W,29000,18,48,Low cost</t>
-  </si>
-  <si>
-    <t>Data,Shared,Alpha VC,25,Alpha Price,55,Alpha Sales 800</t>
-  </si>
-  <si>
-    <t>Data,Shared,Beta VC,40,Beta Price,80,Beta Sales 500</t>
-  </si>
-  <si>
-    <t>Data,Shared,Fixed Cost,28000,,,</t>
-  </si>
-  <si>
-    <t>Question,Raw Data,Q1,Calculate the average fixed cost per month from this data.,,,</t>
-  </si>
-  <si>
-    <t>Question,Raw Data,Q2,Calculate the average variable cost per unit (total variable costs ÷ total units produced).,,,</t>
-  </si>
-  <si>
-    <t>Question,Raw Data,Q3,Using the averages, calculate the contribution margin per unit.,,,</t>
-  </si>
-  <si>
-    <t>Question,Raw Data,Q4,Calculate the breakeven quantity per month using the average values.,,,</t>
-  </si>
-  <si>
-    <t>Question,Raw Data,Q5,Create a clean summary table showing: Average Fixed Cost Average Variable Cost per Unit Selling Price Contribution Margin Breakeven Quantity,,,</t>
-  </si>
-  <si>
-    <t>Question,Raw Data,Q6,Using the actual data for June, calculate the actual profit. Compare with breakeven - did June make a profit?,,,</t>
-  </si>
-  <si>
-    <t>Question,Product Cost,Q7,Calculate the total variable cost per unit for each product.,,,</t>
-  </si>
-  <si>
-    <t>Question,Product Cost,Q8,Calculate the contribution margin per unit for each product.,,,</t>
-  </si>
-  <si>
-    <t>Question,Product Cost,Q9,Calculate the contribution margin percentage for each product.,,,</t>
-  </si>
-  <si>
-    <t>Question,Product Cost,Q10,If total fixed costs for the company are $45,000, calculate the breakeven quantity for each product (assuming only one product is sold).,,,</t>
-  </si>
-  <si>
-    <t>Question,Product Cost,Q11,If the company sells 2,000 units of Product A, 1,200 units of Product B, and 3,500 units of Product C, what is the total profit?,,,</t>
-  </si>
-  <si>
-    <t>Question,Product Cost,Q12,Calculate the weighted average contribution margin based on the sales mix in Q11.,,,</t>
-  </si>
-  <si>
-    <t>Question,Mixed Data,Q13,Clean the data by removing dollar signs and converting all values to numbers. Show the cleaned table.,,,</t>
-  </si>
-  <si>
-    <t>Question,Mixed Data,Q14,Calculate contribution margin for each item using the cleaned data.,,,</t>
-  </si>
-  <si>
-    <t>Question,Mixed Data,Q15,Calculate breakeven quantity for each item.,,,</t>
-  </si>
-  <si>
-    <t>Question,Mixed Data,Q16,Sort the items by breakeven quantity from lowest to highest. Which item is easiest to break even on?,,,</t>
-  </si>
-  <si>
-    <t>Question,Shared Costs,Q17,Calculate the contribution margin for each product.,,,</t>
-  </si>
-  <si>
-    <t>Question,Shared Costs,Q18,Calculate the total contribution margin from both products based on expected sales.,,,</t>
-  </si>
-  <si>
-    <t>Question,Shared Costs,Q19,What is the current monthly profit? (Total Contribution - Fixed Costs),,,</t>
-  </si>
-  <si>
-    <t>Question,Shared Costs,Q20,If the company only sold Product Alpha, how many units would be needed to break even? If only Product Beta, how many units would be needed?,,,</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -181,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -495,196 +419,467 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E48C6ED3-97B4-4C8D-9F4F-FA3770942607}">
-  <dimension ref="A1:A44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Type,Category,Item1,Item2,Item3,Item4,Item5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Data,Monthly,Jan,12500,8200,410,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Data,Monthly,Feb,12800,9100,455,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Data,Monthly,Mar,12400,7800,390,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Data,Monthly,Apr,12900,9800,490,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Data,Monthly,May,12600,8600,430,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Data,Monthly,Jun,13000,10200,510,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Data,Product,A,18,12,5,55</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Data,Product,B,25,15,8,70</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Data,Product,C,10,8,4,32</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Data,Mixed,X,45000,28,65,OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Data,Mixed,Y,38000,22,58,Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Data,Mixed,Z,52000,35,72,High margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Data,Mixed,W,29000,18,48,Low cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Data,Shared,Alpha VC,25,Alpha Price,55,Alpha Sales 800</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Data,Shared,Beta VC,40,Beta Price,80,Beta Sales 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Data,Shared,Fixed Cost,28000,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Question,Raw Data,Q1,Calculate the average fixed cost per month from this data.,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Question,Raw Data,Q2,Calculate the average variable cost per unit (total variable costs ÷ total units produced).,,,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>36</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Preparing Data for Breakeven Analysis,</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Question,Raw Data,Q3,Using the averages, calculate the contribution margin per unit.,,,</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>